--- a/ngan_hang_tu_vung.xlsx
+++ b/ngan_hang_tu_vung.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K315"/>
+  <dimension ref="A1:K311"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3959,260 +3959,261 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C137" t="str">
-        <v>大兴机场见！</v>
+        <v>我读大学了</v>
       </c>
       <c r="D137" t="str">
-        <v>哪个</v>
+        <v>哪里</v>
       </c>
       <c r="E137" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F137" t="str">
-        <v>nǎge</v>
+        <v>nǎlǐ</v>
       </c>
       <c r="G137" t="str">
-        <v>cái nào</v>
+        <v>Ở đâu</v>
       </c>
       <c r="H137" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C138" t="str">
-        <v>我读大学了</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D138" t="str">
-        <v>哪里</v>
+        <v>哪儿</v>
       </c>
       <c r="E138" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F138" t="str">
-        <v>nǎlǐ</v>
+        <v>nǎr</v>
       </c>
       <c r="G138" t="str">
         <v>Ở đâu</v>
       </c>
       <c r="H138" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>7. Địa điểm &amp; Nơi chốn</v>
+      </c>
+    </row>
+    <row r="139" xml:space="preserve">
       <c r="A139">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B139">
-        <v>6</v>
-      </c>
-      <c r="C139" t="str">
-        <v>你的手机号码是多少</v>
+        <v>9.15</v>
+      </c>
+      <c r="C139" t="str" xml:space="preserve">
+        <v xml:space="preserve">我明天上午在学校学习_x000d_
+大兴机场见！</v>
       </c>
       <c r="D139" t="str">
-        <v>哪儿</v>
+        <v>那</v>
       </c>
       <c r="E139" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F139" t="str">
-        <v>nǎr</v>
+        <v>nà</v>
       </c>
       <c r="G139" t="str">
-        <v>Ở đâu</v>
+        <v>Cái đó</v>
       </c>
       <c r="H139" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B140">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C140" t="str">
-        <v>我看了一个电影</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D140" t="str">
-        <v>哪些</v>
+        <v>那边</v>
       </c>
       <c r="E140" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F140" t="str">
-        <v>nǎxiē</v>
+        <v>nàbiān</v>
       </c>
       <c r="G140" t="str">
-        <v>những cái nào</v>
+        <v>ở đó</v>
       </c>
       <c r="H140" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
-      </c>
-    </row>
-    <row r="141" xml:space="preserve">
+        <v>9. Không gian &amp; Vị trí</v>
+      </c>
+    </row>
+    <row r="141">
       <c r="A141">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B141">
-        <v>9.15</v>
-      </c>
-      <c r="C141" t="str" xml:space="preserve">
-        <v xml:space="preserve">我明天上午在学校学习_x000d_
-大兴机场见！</v>
+        <v>11</v>
+      </c>
+      <c r="C141" t="str">
+        <v>我读大学了</v>
       </c>
       <c r="D141" t="str">
-        <v>那</v>
+        <v>那里</v>
       </c>
       <c r="E141" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F141" t="str">
-        <v>nà</v>
+        <v>nàlǐ</v>
       </c>
       <c r="G141" t="str">
-        <v>Cái đó</v>
+        <v>Ở đó</v>
       </c>
       <c r="H141" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B142">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C142" t="str">
-        <v>你的手机号码是多少</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D142" t="str">
-        <v>那边</v>
+        <v>那儿</v>
       </c>
       <c r="E142" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F142" t="str">
-        <v>nàbiān</v>
+        <v>nàr</v>
       </c>
       <c r="G142" t="str">
         <v>ở đó</v>
       </c>
       <c r="H142" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B143">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C143" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D143" t="str">
-        <v>那个</v>
+        <v>男</v>
       </c>
       <c r="E143" t="str">
-        <v>Đại từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F143" t="str">
-        <v>nàge</v>
+        <v>nán</v>
       </c>
       <c r="G143" t="str">
-        <v>cái đó</v>
+        <v>nam giới</v>
       </c>
       <c r="H143" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B144">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C144" t="str">
-        <v>我读大学了</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D144" t="str">
-        <v>那里</v>
+        <v>男朋友</v>
       </c>
       <c r="E144" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F144" t="str">
-        <v>nàlǐ</v>
+        <v>nánpéngyou</v>
       </c>
       <c r="G144" t="str">
-        <v>Ở đó</v>
+        <v>Bạn trai</v>
       </c>
       <c r="H144" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>1. Con người &amp; Các mối quan hệ</v>
+      </c>
+    </row>
+    <row r="145" xml:space="preserve">
       <c r="A145">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B145">
-        <v>10</v>
-      </c>
-      <c r="C145" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>4.7</v>
+      </c>
+      <c r="C145" t="str" xml:space="preserve">
+        <v xml:space="preserve">我有两个孩子_x000d_
+我晚上六点半下班</v>
       </c>
       <c r="D145" t="str">
-        <v>那儿</v>
+        <v>呢</v>
       </c>
       <c r="E145" t="str">
-        <v>Đại từ</v>
+        <v>Trợ từ</v>
       </c>
       <c r="F145" t="str">
-        <v>nàr</v>
+        <v>ne</v>
       </c>
       <c r="G145" t="str">
-        <v>ở đó</v>
+        <v>Trợ từ đặt cuối câu để khẳng định</v>
       </c>
       <c r="H145" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C146" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D146" t="str">
-        <v>那些</v>
+        <v>能</v>
       </c>
       <c r="E146" t="str">
-        <v>Đại từ</v>
+        <v>Động từ năng nguyện</v>
       </c>
       <c r="F146" t="str">
-        <v>nàxiē</v>
+        <v>néng</v>
       </c>
       <c r="G146" t="str">
-        <v>Những cái đó</v>
+        <v>có thể</v>
       </c>
       <c r="H146" t="str">
         <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
@@ -4220,25 +4221,25 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B147">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C147" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我叫李文</v>
       </c>
       <c r="D147" t="str">
-        <v>男</v>
+        <v>你</v>
       </c>
       <c r="E147" t="str">
-        <v>Tính từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F147" t="str">
-        <v>nán</v>
+        <v>nǐ</v>
       </c>
       <c r="G147" t="str">
-        <v>nam giới</v>
+        <v>Bạn</v>
       </c>
       <c r="H147" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
@@ -4246,101 +4247,97 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B148">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C148" t="str">
-        <v>大兴机场见！</v>
+        <v>AI 小语，你好！</v>
       </c>
       <c r="D148" t="str">
-        <v>男朋友</v>
-      </c>
-      <c r="E148" t="str">
-        <v>Danh từ</v>
+        <v>你好</v>
       </c>
       <c r="F148" t="str">
-        <v>nánpéngyou</v>
+        <v>nǐ hǎo</v>
       </c>
       <c r="G148" t="str">
-        <v>Bạn trai</v>
+        <v>Xin chào</v>
       </c>
       <c r="H148" t="str">
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>152</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149" t="str">
+        <v>AI 小语，你好！</v>
+      </c>
+      <c r="D149" t="str">
+        <v>你们</v>
+      </c>
+      <c r="E149" t="str">
+        <v>Đại từ</v>
+      </c>
+      <c r="F149" t="str">
+        <v>nǐmen</v>
+      </c>
+      <c r="G149" t="str">
+        <v>Bạn</v>
+      </c>
+      <c r="H149" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
-      </c>
-    </row>
-    <row r="149" xml:space="preserve">
-      <c r="A149">
-        <v>148</v>
-      </c>
-      <c r="B149">
-        <v>4.7</v>
-      </c>
-      <c r="C149" t="str" xml:space="preserve">
-        <v xml:space="preserve">我有两个孩子_x000d_
-我晚上六点半下班</v>
-      </c>
-      <c r="D149" t="str">
-        <v>呢</v>
-      </c>
-      <c r="E149" t="str">
-        <v>Trợ từ</v>
-      </c>
-      <c r="F149" t="str">
-        <v>ne</v>
-      </c>
-      <c r="G149" t="str">
-        <v>Trợ từ đặt cuối câu để khẳng định</v>
-      </c>
-      <c r="H149" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B150">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C150" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D150" t="str">
-        <v>能</v>
+        <v>年</v>
       </c>
       <c r="E150" t="str">
-        <v>Động từ năng nguyện</v>
+        <v>Danh từ</v>
       </c>
       <c r="F150" t="str">
-        <v>néng</v>
+        <v>nián</v>
       </c>
       <c r="G150" t="str">
-        <v>có thể</v>
+        <v>Năm</v>
       </c>
       <c r="H150" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151" t="str">
-        <v>我叫李文</v>
+        <v>AI 小语，你好！</v>
       </c>
       <c r="D151" t="str">
-        <v>你</v>
+        <v>您</v>
       </c>
       <c r="E151" t="str">
-        <v>Danh từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F151" t="str">
-        <v>nǐ</v>
+        <v>nín</v>
       </c>
       <c r="G151" t="str">
         <v>Bạn</v>
@@ -4351,48 +4348,51 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C152" t="str">
-        <v>AI 小语，你好！</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D152" t="str">
-        <v>你好</v>
+        <v>牛奶</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Danh từ</v>
       </c>
       <c r="F152" t="str">
-        <v>nǐ hǎo</v>
+        <v>niúnǎi</v>
       </c>
       <c r="G152" t="str">
-        <v>Xin chào</v>
+        <v>sữa</v>
       </c>
       <c r="H152" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>16. Đồ ăn &amp; Thức uống</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C153" t="str">
-        <v>AI 小语，你好！</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D153" t="str">
-        <v>你们</v>
+        <v>女</v>
       </c>
       <c r="E153" t="str">
-        <v>Đại từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F153" t="str">
-        <v>nǐmen</v>
+        <v>nǚ</v>
       </c>
       <c r="G153" t="str">
-        <v>Bạn</v>
+        <v>nữ giới</v>
       </c>
       <c r="H153" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
@@ -4400,51 +4400,51 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B154">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C154" t="str">
-        <v>大兴机场见！</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D154" t="str">
-        <v>年</v>
+        <v>女儿</v>
       </c>
       <c r="E154" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F154" t="str">
-        <v>nián</v>
+        <v>nǚ’ér</v>
       </c>
       <c r="G154" t="str">
-        <v>Năm</v>
+        <v>con gái</v>
       </c>
       <c r="H154" t="str">
-        <v>10. Thời gian</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C155" t="str">
-        <v>AI 小语，你好！</v>
+        <v>我是中国人</v>
       </c>
       <c r="D155" t="str">
-        <v>您</v>
+        <v>女朋友</v>
       </c>
       <c r="E155" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F155" t="str">
-        <v>nín</v>
+        <v>nǚpéngyou</v>
       </c>
       <c r="G155" t="str">
-        <v>Bạn</v>
+        <v>bạn gái</v>
       </c>
       <c r="H155" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
@@ -4452,51 +4452,51 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B156">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C156" t="str">
-        <v>你的手机号码是多少</v>
+        <v>请给我一杯茶</v>
       </c>
       <c r="D156" t="str">
-        <v>牛奶</v>
+        <v>女士</v>
       </c>
       <c r="E156" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F156" t="str">
-        <v>niúnǎi</v>
+        <v>nǚshì</v>
       </c>
       <c r="G156" t="str">
-        <v>sữa</v>
+        <v>Cô</v>
       </c>
       <c r="H156" t="str">
-        <v>16. Đồ ăn &amp; Thức uống</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B157">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C157" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D157" t="str">
-        <v>女</v>
+        <v>朋友</v>
       </c>
       <c r="E157" t="str">
-        <v>Tính từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F157" t="str">
-        <v>nǚ</v>
+        <v>péngyou</v>
       </c>
       <c r="G157" t="str">
-        <v>nữ giới</v>
+        <v>bạn bè</v>
       </c>
       <c r="H157" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
@@ -4504,441 +4504,441 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C158" t="str">
-        <v>我有两个孩子</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D158" t="str">
-        <v>女儿</v>
+        <v>便宜</v>
       </c>
       <c r="E158" t="str">
-        <v>Danh từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F158" t="str">
-        <v>nǚ’ér</v>
+        <v>piányi</v>
       </c>
       <c r="G158" t="str">
-        <v>con gái</v>
+        <v>Rẻ</v>
       </c>
       <c r="H158" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B159">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C159" t="str">
-        <v>我是中国人</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D159" t="str">
-        <v>女朋友</v>
+        <v>漂亮</v>
       </c>
       <c r="E159" t="str">
-        <v>Danh từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F159" t="str">
-        <v>nǚpéngyou</v>
+        <v>piàoliang</v>
       </c>
       <c r="G159" t="str">
-        <v>bạn gái</v>
+        <v>đẹp</v>
       </c>
       <c r="H159" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B160">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C160" t="str">
-        <v>请给我一杯茶</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D160" t="str">
-        <v>女士</v>
+        <v>苹果</v>
       </c>
       <c r="E160" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F160" t="str">
-        <v>nǚshì</v>
+        <v>píngguǒ</v>
       </c>
       <c r="G160" t="str">
-        <v>Cô</v>
+        <v>quả táo</v>
       </c>
       <c r="H160" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>16. Đồ ăn &amp; Thức uống</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B161">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C161" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D161" t="str">
-        <v>朋友</v>
+        <v>七</v>
       </c>
       <c r="E161" t="str">
-        <v>Danh từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F161" t="str">
-        <v>péngyou</v>
+        <v>qī</v>
       </c>
       <c r="G161" t="str">
-        <v>bạn bè</v>
+        <v>bảy</v>
       </c>
       <c r="H161" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B162">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C162" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我读大学了</v>
       </c>
       <c r="D162" t="str">
-        <v>便宜</v>
+        <v>起床</v>
       </c>
       <c r="E162" t="str">
-        <v>Tính từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F162" t="str">
-        <v>piányi</v>
+        <v>qǐchuáng</v>
       </c>
       <c r="G162" t="str">
-        <v>Rẻ</v>
+        <v>thức dậy</v>
       </c>
       <c r="H162" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B163">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C163" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D163" t="str">
-        <v>漂亮</v>
+        <v>千</v>
       </c>
       <c r="E163" t="str">
-        <v>Tính từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F163" t="str">
-        <v>piàoliang</v>
+        <v>qiān</v>
       </c>
       <c r="G163" t="str">
-        <v>đẹp</v>
+        <v>nghìn</v>
       </c>
       <c r="H163" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B164">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C164" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D164" t="str">
-        <v>苹果</v>
+        <v>前</v>
       </c>
       <c r="E164" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F164" t="str">
-        <v>píngguǒ</v>
+        <v>qián</v>
       </c>
       <c r="G164" t="str">
-        <v>quả táo</v>
+        <v>phía trước</v>
       </c>
       <c r="H164" t="str">
-        <v>16. Đồ ăn &amp; Thức uống</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B165">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C165" t="str">
-        <v>我有两个孩子</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D165" t="str">
-        <v>七</v>
+        <v>前边</v>
       </c>
       <c r="E165" t="str">
-        <v>Số từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F165" t="str">
-        <v>qī</v>
+        <v>qiánbiān</v>
       </c>
       <c r="G165" t="str">
-        <v>bảy</v>
+        <v>đằng trước</v>
       </c>
       <c r="H165" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B166">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C166" t="str">
-        <v>我读大学了</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D166" t="str">
-        <v>起床</v>
+        <v>钱</v>
       </c>
       <c r="E166" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F166" t="str">
-        <v>qǐchuáng</v>
+        <v>qián</v>
       </c>
       <c r="G166" t="str">
-        <v>thức dậy</v>
+        <v>tiền bạc</v>
       </c>
       <c r="H166" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B167">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C167" t="str">
-        <v>我有两个孩子</v>
+        <v>请给我一杯茶</v>
       </c>
       <c r="D167" t="str">
-        <v>千</v>
+        <v>请</v>
       </c>
       <c r="E167" t="str">
-        <v>Số từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F167" t="str">
-        <v>qiān</v>
+        <v>qǐng</v>
       </c>
       <c r="G167" t="str">
-        <v>nghìn</v>
+        <v>Xin vui lòng</v>
       </c>
       <c r="H167" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B168">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C168" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我叫李文</v>
       </c>
       <c r="D168" t="str">
-        <v>前</v>
+        <v>请问</v>
       </c>
       <c r="E168" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F168" t="str">
-        <v>qián</v>
+        <v>qǐngwèn</v>
       </c>
       <c r="G168" t="str">
-        <v>phía trước</v>
+        <v>cho hỏi, xin hỏi</v>
       </c>
       <c r="H168" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B169">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C169" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D169" t="str">
-        <v>前边</v>
+        <v>去</v>
       </c>
       <c r="E169" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F169" t="str">
-        <v>qiánbiān</v>
+        <v>qù</v>
       </c>
       <c r="G169" t="str">
-        <v>đằng trước</v>
+        <v>đi</v>
       </c>
       <c r="H169" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>8. Giao thông &amp; Di chuyển</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B170">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C170" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D170" t="str">
-        <v>钱</v>
+        <v>去年</v>
       </c>
       <c r="E170" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F170" t="str">
-        <v>qián</v>
+        <v>qùnián</v>
       </c>
       <c r="G170" t="str">
-        <v>tiền bạc</v>
+        <v>năm ngoái</v>
       </c>
       <c r="H170" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B171">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C171" t="str">
-        <v>请给我一杯茶</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D171" t="str">
-        <v>请</v>
+        <v>热</v>
       </c>
       <c r="E171" t="str">
-        <v>Động từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F171" t="str">
-        <v>qǐng</v>
+        <v>rè</v>
       </c>
       <c r="G171" t="str">
-        <v>Xin vui lòng</v>
+        <v>nóng</v>
       </c>
       <c r="H171" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C172" t="str">
-        <v>我叫李文</v>
+        <v>我是中国人</v>
       </c>
       <c r="D172" t="str">
-        <v>请问</v>
+        <v>人</v>
       </c>
       <c r="E172" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F172" t="str">
-        <v>qǐngwèn</v>
+        <v>rén</v>
       </c>
       <c r="G172" t="str">
-        <v>cho hỏi, xin hỏi</v>
+        <v>mọi người</v>
       </c>
       <c r="H172" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B173">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C173" t="str">
-        <v>你的手机号码是多少</v>
+        <v>我叫李文</v>
       </c>
       <c r="D173" t="str">
-        <v>去</v>
+        <v>认识</v>
       </c>
       <c r="E173" t="str">
         <v>Động từ</v>
       </c>
       <c r="F173" t="str">
-        <v>qù</v>
+        <v>rènshi</v>
       </c>
       <c r="G173" t="str">
-        <v>đi</v>
+        <v>biết</v>
       </c>
       <c r="H173" t="str">
-        <v>8. Giao thông &amp; Di chuyển</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B174">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C174" t="str">
-        <v>大兴机场见！</v>
+        <v>今天我休息</v>
       </c>
       <c r="D174" t="str">
-        <v>去年</v>
+        <v>日</v>
       </c>
       <c r="E174" t="str">
-        <v>Danh từ</v>
+        <v>Lượng từ</v>
       </c>
       <c r="F174" t="str">
-        <v>qùnián</v>
+        <v>rì</v>
       </c>
       <c r="G174" t="str">
-        <v>năm ngoái</v>
+        <v>ngày</v>
       </c>
       <c r="H174" t="str">
         <v>10. Thời gian</v>
@@ -4946,495 +4946,495 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B175">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C175" t="str">
-        <v>昨天下雪了</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D175" t="str">
-        <v>热</v>
+        <v>三</v>
       </c>
       <c r="E175" t="str">
-        <v>Tính từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F175" t="str">
-        <v>rè</v>
+        <v>sān</v>
       </c>
       <c r="G175" t="str">
-        <v>nóng</v>
+        <v>ba</v>
       </c>
       <c r="H175" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B176">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C176" t="str">
-        <v>我是中国人</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D176" t="str">
-        <v>人</v>
+        <v>商店</v>
       </c>
       <c r="E176" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F176" t="str">
-        <v>rén</v>
+        <v>shāngdiàn</v>
       </c>
       <c r="G176" t="str">
-        <v>mọi người</v>
+        <v>cửa hàng</v>
       </c>
       <c r="H176" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>7. Địa điểm &amp; Nơi chốn</v>
+      </c>
+    </row>
+    <row r="177" xml:space="preserve">
       <c r="A177">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B177">
-        <v>2</v>
-      </c>
-      <c r="C177" t="str">
-        <v>我叫李文</v>
+        <v>9.14</v>
+      </c>
+      <c r="C177" t="str" xml:space="preserve">
+        <v xml:space="preserve">我明天上午在学校学习_x000d_
+我看了一个电影</v>
       </c>
       <c r="D177" t="str">
-        <v>认识</v>
+        <v>上</v>
       </c>
       <c r="E177" t="str">
-        <v>Động từ</v>
+        <v>Danh từ, Động từ</v>
       </c>
       <c r="F177" t="str">
-        <v>rènshi</v>
-      </c>
-      <c r="G177" t="str">
-        <v>biết</v>
+        <v>shàng</v>
+      </c>
+      <c r="G177" t="str" xml:space="preserve">
+        <v xml:space="preserve">danh từ - vị trí cao (trên bảng xếp hạng)_x000d_
+động từ - lên; bắt đầu làm gì đó ở mốc thời gian cố định</v>
       </c>
       <c r="H177" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B178">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C178" t="str">
-        <v>今天我休息</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D178" t="str">
-        <v>日</v>
+        <v>上班</v>
       </c>
       <c r="E178" t="str">
-        <v>Lượng từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F178" t="str">
-        <v>rì</v>
+        <v>shàngbān</v>
       </c>
       <c r="G178" t="str">
-        <v>ngày</v>
+        <v>công việc</v>
       </c>
       <c r="H178" t="str">
-        <v>10. Thời gian</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B179">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C179" t="str">
-        <v>我有两个孩子</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D179" t="str">
-        <v>三</v>
+        <v>上课</v>
       </c>
       <c r="E179" t="str">
-        <v>Số từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F179" t="str">
-        <v>sān</v>
+        <v>shàngkè</v>
       </c>
       <c r="G179" t="str">
-        <v>ba</v>
+        <v>Tham gia lớp học</v>
       </c>
       <c r="H179" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B180">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C180" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D180" t="str">
-        <v>商店</v>
+        <v>上午</v>
       </c>
       <c r="E180" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F180" t="str">
-        <v>shāngdiàn</v>
+        <v>shàngwǔ</v>
       </c>
       <c r="G180" t="str">
-        <v>cửa hàng</v>
+        <v>buổi sáng</v>
       </c>
       <c r="H180" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
-      </c>
-    </row>
-    <row r="181" xml:space="preserve">
+        <v>10. Thời gian</v>
+      </c>
+    </row>
+    <row r="181">
       <c r="A181">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B181">
-        <v>9.14</v>
-      </c>
-      <c r="C181" t="str" xml:space="preserve">
-        <v xml:space="preserve">我明天上午在学校学习_x000d_
-我看了一个电影</v>
+        <v>14</v>
+      </c>
+      <c r="C181" t="str">
+        <v>我看了一个电影</v>
       </c>
       <c r="D181" t="str">
-        <v>上</v>
+        <v>上学</v>
       </c>
       <c r="E181" t="str">
-        <v>Danh từ, Động từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F181" t="str">
-        <v>shàng</v>
-      </c>
-      <c r="G181" t="str" xml:space="preserve">
-        <v xml:space="preserve">danh từ - vị trí cao (trên bảng xếp hạng)_x000d_
-động từ - lên; bắt đầu làm gì đó ở mốc thời gian cố định</v>
+        <v>shàngxué</v>
+      </c>
+      <c r="G181" t="str">
+        <v>đi học</v>
       </c>
       <c r="H181" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B182">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C182" t="str">
-        <v>我晚上六点半下班</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D182" t="str">
-        <v>上班</v>
+        <v>少</v>
       </c>
       <c r="E182" t="str">
-        <v>Động từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F182" t="str">
-        <v>shàngbān</v>
+        <v>shǎo</v>
       </c>
       <c r="G182" t="str">
-        <v>công việc</v>
+        <v>một vài</v>
       </c>
       <c r="H182" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B183">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C183" t="str">
-        <v>我晚上六点半下班</v>
+        <v>我是中国人</v>
       </c>
       <c r="D183" t="str">
-        <v>上课</v>
+        <v>谁</v>
       </c>
       <c r="E183" t="str">
-        <v>Động từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F183" t="str">
-        <v>shàngkè</v>
+        <v>shéi/shuí</v>
       </c>
       <c r="G183" t="str">
-        <v>Tham gia lớp học</v>
+        <v>Ai</v>
       </c>
       <c r="H183" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B184">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C184" t="str">
-        <v>我晚上六点半下班</v>
+        <v>我叫李文</v>
       </c>
       <c r="D184" t="str">
-        <v>上午</v>
+        <v>什么</v>
       </c>
       <c r="E184" t="str">
-        <v>Danh từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F184" t="str">
-        <v>shàngwǔ</v>
+        <v>shénme</v>
       </c>
       <c r="G184" t="str">
-        <v>buổi sáng</v>
+        <v>Cái gì</v>
       </c>
       <c r="H184" t="str">
-        <v>10. Thời gian</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C185" t="str">
-        <v>我看了一个电影</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D185" t="str">
-        <v>上学</v>
+        <v>生病</v>
       </c>
       <c r="E185" t="str">
         <v>Động từ</v>
       </c>
       <c r="F185" t="str">
-        <v>shàngxué</v>
+        <v>shēngbìng</v>
       </c>
       <c r="G185" t="str">
-        <v>đi học</v>
+        <v>Bị ốm</v>
       </c>
       <c r="H185" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>2. Cơ thể &amp; Sức khỏe</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B186">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C186" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D186" t="str">
-        <v>少</v>
+        <v>十</v>
       </c>
       <c r="E186" t="str">
-        <v>Tính từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F186" t="str">
-        <v>shǎo</v>
+        <v>shí</v>
       </c>
       <c r="G186" t="str">
-        <v>một vài</v>
+        <v>mười</v>
       </c>
       <c r="H186" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B187">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C187" t="str">
-        <v>我是中国人</v>
+        <v>我读大学了</v>
       </c>
       <c r="D187" t="str">
-        <v>谁</v>
+        <v>时候</v>
       </c>
       <c r="E187" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F187" t="str">
-        <v>shéi/shuí</v>
+        <v>shíhou</v>
       </c>
       <c r="G187" t="str">
-        <v>Ai</v>
+        <v>khi</v>
       </c>
       <c r="H187" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C188" t="str">
-        <v>我叫李文</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D188" t="str">
-        <v>什么</v>
+        <v>时间</v>
       </c>
       <c r="E188" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F188" t="str">
-        <v>shénme</v>
+        <v>shíjiān</v>
       </c>
       <c r="G188" t="str">
-        <v>Cái gì</v>
+        <v>thời gian</v>
       </c>
       <c r="H188" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B189">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C189" t="str">
-        <v>昨天下雪了</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D189" t="str">
-        <v>生病</v>
+        <v>事</v>
       </c>
       <c r="E189" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F189" t="str">
-        <v>shēngbìng</v>
+        <v>shì</v>
       </c>
       <c r="G189" t="str">
-        <v>Bị ốm</v>
+        <v>điều</v>
       </c>
       <c r="H189" t="str">
-        <v>2. Cơ thể &amp; Sức khỏe</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B190">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C190" t="str">
-        <v>我有两个孩子</v>
+        <v>我叫李文</v>
       </c>
       <c r="D190" t="str">
-        <v>十</v>
+        <v>是</v>
       </c>
       <c r="E190" t="str">
-        <v>Số từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F190" t="str">
-        <v>shí</v>
+        <v>shì</v>
       </c>
       <c r="G190" t="str">
-        <v>mười</v>
+        <v>Đúng</v>
       </c>
       <c r="H190" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B191">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C191" t="str">
-        <v>我读大学了</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D191" t="str">
-        <v>时候</v>
+        <v>手机</v>
       </c>
       <c r="E191" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F191" t="str">
-        <v>shíhou</v>
+        <v>shǒujī</v>
       </c>
       <c r="G191" t="str">
-        <v>khi</v>
+        <v>điện thoại di động</v>
       </c>
       <c r="H191" t="str">
-        <v>10. Thời gian</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B192">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C192" t="str">
-        <v>大兴机场见！</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D192" t="str">
-        <v>时间</v>
+        <v>售货员</v>
       </c>
       <c r="E192" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F192" t="str">
-        <v>shíjiān</v>
+        <v>shòuhuòyuán</v>
       </c>
       <c r="G192" t="str">
-        <v>thời gian</v>
+        <v>Nhân viên bán hàng</v>
       </c>
       <c r="H192" t="str">
-        <v>10. Thời gian</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B193">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C193" t="str">
-        <v>我晚上六点半下班</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D193" t="str">
-        <v>事</v>
+        <v>书</v>
       </c>
       <c r="E193" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F193" t="str">
-        <v>shì</v>
+        <v>shū</v>
       </c>
       <c r="G193" t="str">
-        <v>điều</v>
+        <v>Sách</v>
       </c>
       <c r="H193" t="str">
         <v>6. Đồ vật &amp; Công cụ</v>
@@ -5442,59 +5442,59 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B194">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C194" t="str">
-        <v>我叫李文</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D194" t="str">
-        <v>是</v>
+        <v>书店</v>
       </c>
       <c r="E194" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F194" t="str">
-        <v>shì</v>
+        <v>shūdiàn</v>
       </c>
       <c r="G194" t="str">
-        <v>Đúng</v>
+        <v>hiệu sách</v>
       </c>
       <c r="H194" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B195">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C195" t="str">
-        <v>你的手机号码是多少</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D195" t="str">
-        <v>手机</v>
+        <v>水</v>
       </c>
       <c r="E195" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F195" t="str">
-        <v>shǒujī</v>
+        <v>shuǐ</v>
       </c>
       <c r="G195" t="str">
-        <v>điện thoại di động</v>
+        <v>Nước</v>
       </c>
       <c r="H195" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>15. Tự nhiên</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B196">
         <v>10</v>
@@ -5503,206 +5503,206 @@
         <v>这儿的苹果真便宜</v>
       </c>
       <c r="D196" t="str">
-        <v>售货员</v>
+        <v>水果</v>
       </c>
       <c r="E196" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F196" t="str">
-        <v>shòuhuòyuán</v>
+        <v>shuǐguǒ</v>
       </c>
       <c r="G196" t="str">
-        <v>Nhân viên bán hàng</v>
+        <v>hoa quả</v>
       </c>
       <c r="H196" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>16. Đồ ăn &amp; Thức uống</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B197">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C197" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我读大学了</v>
       </c>
       <c r="D197" t="str">
-        <v>书</v>
+        <v>睡</v>
       </c>
       <c r="E197" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F197" t="str">
-        <v>shū</v>
+        <v>shuì</v>
       </c>
       <c r="G197" t="str">
-        <v>Sách</v>
+        <v>ngủ</v>
       </c>
       <c r="H197" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B198">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C198" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我读大学了</v>
       </c>
       <c r="D198" t="str">
-        <v>书店</v>
+        <v>睡觉</v>
       </c>
       <c r="E198" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F198" t="str">
-        <v>shūdiàn</v>
+        <v>shuìjiào</v>
       </c>
       <c r="G198" t="str">
-        <v>hiệu sách</v>
+        <v>ngủ</v>
       </c>
       <c r="H198" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B199">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C199" t="str">
-        <v>昨天下雪了</v>
+        <v>我读大学了</v>
       </c>
       <c r="D199" t="str">
-        <v>水</v>
+        <v>说</v>
       </c>
       <c r="E199" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F199" t="str">
-        <v>shuǐ</v>
+        <v>shuō</v>
       </c>
       <c r="G199" t="str">
-        <v>Nước</v>
+        <v>nói</v>
       </c>
       <c r="H199" t="str">
-        <v>15. Tự nhiên</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B200">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C200" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D200" t="str">
-        <v>水果</v>
+        <v>说话</v>
       </c>
       <c r="E200" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F200" t="str">
-        <v>shuǐguǒ</v>
+        <v>shuōhuà</v>
       </c>
       <c r="G200" t="str">
-        <v>hoa quả</v>
+        <v>nói</v>
       </c>
       <c r="H200" t="str">
-        <v>16. Đồ ăn &amp; Thức uống</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B201">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C201" t="str">
-        <v>我读大学了</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D201" t="str">
-        <v>睡</v>
+        <v>四</v>
       </c>
       <c r="E201" t="str">
-        <v>Động từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F201" t="str">
-        <v>shuì</v>
+        <v>sì</v>
       </c>
       <c r="G201" t="str">
-        <v>ngủ</v>
+        <v>Bốn</v>
       </c>
       <c r="H201" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B202">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C202" t="str">
-        <v>我读大学了</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D202" t="str">
-        <v>睡觉</v>
+        <v>岁</v>
       </c>
       <c r="E202" t="str">
-        <v>Động từ</v>
+        <v>Lượng từ</v>
       </c>
       <c r="F202" t="str">
-        <v>shuìjiào</v>
+        <v>suì</v>
       </c>
       <c r="G202" t="str">
-        <v>ngủ</v>
+        <v>tuổi</v>
       </c>
       <c r="H202" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B203">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C203" t="str">
-        <v>我读大学了</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D203" t="str">
-        <v>说</v>
+        <v>他</v>
       </c>
       <c r="E203" t="str">
-        <v>Động từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F203" t="str">
-        <v>shuō</v>
+        <v>tā</v>
       </c>
       <c r="G203" t="str">
-        <v>nói</v>
+        <v>Anh ta</v>
       </c>
       <c r="H203" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B204">
         <v>14</v>
@@ -5711,94 +5711,88 @@
         <v>我看了一个电影</v>
       </c>
       <c r="D204" t="str">
-        <v>说话</v>
+        <v>他们</v>
       </c>
       <c r="E204" t="str">
-        <v>Động từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F204" t="str">
-        <v>shuōhuà</v>
+        <v>tāmen</v>
       </c>
       <c r="G204" t="str">
-        <v>nói</v>
+        <v>họ</v>
       </c>
       <c r="H204" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B205">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C205" t="str">
-        <v>我有两个孩子</v>
+        <v>今天我休息</v>
       </c>
       <c r="D205" t="str">
-        <v>四</v>
+        <v>它</v>
       </c>
       <c r="E205" t="str">
-        <v>Số từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F205" t="str">
-        <v>sì</v>
+        <v>tā</v>
       </c>
       <c r="G205" t="str">
-        <v>Bốn</v>
+        <v>Nó</v>
       </c>
       <c r="H205" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>205</v>
-      </c>
-      <c r="B206">
-        <v>4</v>
-      </c>
-      <c r="C206" t="str">
-        <v>我有两个孩子</v>
+        <v>209</v>
       </c>
       <c r="D206" t="str">
-        <v>岁</v>
+        <v>它们</v>
       </c>
       <c r="E206" t="str">
-        <v>Lượng từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F206" t="str">
-        <v>suì</v>
+        <v>tāmen</v>
       </c>
       <c r="G206" t="str">
-        <v>tuổi</v>
+        <v>họ</v>
       </c>
       <c r="H206" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B207">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C207" t="str">
-        <v>我有两个孩子</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D207" t="str">
-        <v>他</v>
+        <v>她们</v>
       </c>
       <c r="E207" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F207" t="str">
-        <v>tā</v>
+        <v>tāmen</v>
       </c>
       <c r="G207" t="str">
-        <v>Anh ta</v>
+        <v>họ</v>
       </c>
       <c r="H207" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
@@ -5806,79 +5800,85 @@
     </row>
     <row r="208">
       <c r="A208">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B208">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C208" t="str">
-        <v>我看了一个电影</v>
+        <v>我是中国人</v>
       </c>
       <c r="D208" t="str">
-        <v>他们</v>
+        <v>太</v>
       </c>
       <c r="E208" t="str">
-        <v>Đại từ</v>
+        <v>Phó từ</v>
       </c>
       <c r="F208" t="str">
-        <v>tāmen</v>
+        <v>tài</v>
       </c>
       <c r="G208" t="str">
-        <v>họ</v>
+        <v>cũng vậy</v>
       </c>
       <c r="H208" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B209">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C209" t="str">
-        <v>今天我休息</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D209" t="str">
-        <v>它</v>
+        <v>天</v>
       </c>
       <c r="E209" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ, Lượng từ</v>
       </c>
       <c r="F209" t="str">
-        <v>tā</v>
+        <v>tiān</v>
       </c>
       <c r="G209" t="str">
-        <v>Nó</v>
+        <v>thời tiết, ngày</v>
       </c>
       <c r="H209" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>15. Tự nhiên</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>209</v>
+        <v>213</v>
+      </c>
+      <c r="B210">
+        <v>12</v>
+      </c>
+      <c r="C210" t="str">
+        <v>昨天下雪了</v>
       </c>
       <c r="D210" t="str">
-        <v>它们</v>
+        <v>天气</v>
       </c>
       <c r="E210" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F210" t="str">
-        <v>tāmen</v>
+        <v>tiānqì</v>
       </c>
       <c r="G210" t="str">
-        <v>họ</v>
+        <v>thời tiết</v>
       </c>
       <c r="H210" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>15. Tự nhiên</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B211">
         <v>14</v>
@@ -5887,336 +5887,336 @@
         <v>我看了一个电影</v>
       </c>
       <c r="D211" t="str">
-        <v>她们</v>
+        <v>听</v>
       </c>
       <c r="E211" t="str">
-        <v>Đại từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F211" t="str">
-        <v>tāmen</v>
+        <v>tīng</v>
       </c>
       <c r="G211" t="str">
-        <v>họ</v>
+        <v>Nghe</v>
       </c>
       <c r="H211" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B212">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C212" t="str">
-        <v>我是中国人</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D212" t="str">
-        <v>太</v>
+        <v>听见</v>
       </c>
       <c r="E212" t="str">
-        <v>Phó từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F212" t="str">
-        <v>tài</v>
+        <v>tīngjiàn</v>
       </c>
       <c r="G212" t="str">
-        <v>cũng vậy</v>
+        <v>nghe</v>
       </c>
       <c r="H212" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B213">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C213" t="str">
-        <v>昨天下雪了</v>
+        <v>AI 小语，你好！</v>
       </c>
       <c r="D213" t="str">
-        <v>天</v>
+        <v>同学</v>
       </c>
       <c r="E213" t="str">
-        <v>Danh từ, Lượng từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F213" t="str">
-        <v>tiān</v>
+        <v>tóngxué</v>
       </c>
       <c r="G213" t="str">
-        <v>thời tiết, ngày</v>
+        <v>bạn cùng lớp</v>
       </c>
       <c r="H213" t="str">
-        <v>15. Tự nhiên</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B214">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C214" t="str">
-        <v>昨天下雪了</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D214" t="str">
-        <v>天气</v>
+        <v>外</v>
       </c>
       <c r="E214" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F214" t="str">
-        <v>tiānqì</v>
+        <v>wài</v>
       </c>
       <c r="G214" t="str">
-        <v>thời tiết</v>
+        <v>ngoài</v>
       </c>
       <c r="H214" t="str">
-        <v>15. Tự nhiên</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B215">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C215" t="str">
-        <v>我看了一个电影</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D215" t="str">
-        <v>听</v>
+        <v>外边</v>
       </c>
       <c r="E215" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F215" t="str">
-        <v>tīng</v>
+        <v>wàibiān</v>
       </c>
       <c r="G215" t="str">
-        <v>Nghe</v>
+        <v>ngoài</v>
       </c>
       <c r="H215" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B216">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C216" t="str">
-        <v>我看了一个电影</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D216" t="str">
-        <v>听见</v>
+        <v>玩</v>
       </c>
       <c r="E216" t="str">
         <v>Động từ</v>
       </c>
       <c r="F216" t="str">
-        <v>tīngjiàn</v>
+        <v>wán</v>
       </c>
       <c r="G216" t="str">
-        <v>nghe</v>
+        <v>Chơi</v>
       </c>
       <c r="H216" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C217" t="str">
-        <v>AI 小语，你好！</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D217" t="str">
-        <v>同学</v>
+        <v>晚</v>
       </c>
       <c r="E217" t="str">
-        <v>Danh từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F217" t="str">
-        <v>tóngxué</v>
+        <v>wǎn</v>
       </c>
       <c r="G217" t="str">
-        <v>bạn cùng lớp</v>
+        <v>Đêm</v>
       </c>
       <c r="H217" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B218">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C218" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D218" t="str">
-        <v>外</v>
+        <v>晚饭</v>
       </c>
       <c r="E218" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F218" t="str">
-        <v>wài</v>
+        <v>wǎnfàn</v>
       </c>
       <c r="G218" t="str">
-        <v>ngoài</v>
+        <v>bữa tối</v>
       </c>
       <c r="H218" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>16. Đồ ăn &amp; Thức uống</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B219">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C219" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D219" t="str">
-        <v>外边</v>
+        <v>晚上</v>
       </c>
       <c r="E219" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F219" t="str">
-        <v>wàibiān</v>
+        <v>wǎnshang</v>
       </c>
       <c r="G219" t="str">
-        <v>ngoài</v>
+        <v>đêm</v>
       </c>
       <c r="H219" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B220">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C220" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我是中国人</v>
       </c>
       <c r="D220" t="str">
-        <v>玩</v>
+        <v>喂</v>
       </c>
       <c r="E220" t="str">
-        <v>Động từ</v>
+        <v>Thán từ</v>
       </c>
       <c r="F220" t="str">
-        <v>wán</v>
+        <v>wèi</v>
       </c>
       <c r="G220" t="str">
-        <v>Chơi</v>
+        <v>Xin chào</v>
       </c>
       <c r="H220" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B221">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C221" t="str">
-        <v>我看了一个电影</v>
+        <v>我读大学了</v>
       </c>
       <c r="D221" t="str">
-        <v>晚</v>
+        <v>问</v>
       </c>
       <c r="E221" t="str">
-        <v>Tính từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F221" t="str">
-        <v>wǎn</v>
+        <v>wèn</v>
       </c>
       <c r="G221" t="str">
-        <v>Đêm</v>
+        <v>hỏi</v>
       </c>
       <c r="H221" t="str">
-        <v>10. Thời gian</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B222">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C222" t="str">
-        <v>你的手机号码是多少</v>
+        <v>请给我一杯茶</v>
       </c>
       <c r="D222" t="str">
-        <v>晚饭</v>
+        <v>问题</v>
       </c>
       <c r="E222" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F222" t="str">
-        <v>wǎnfàn</v>
+        <v>wèntí</v>
       </c>
       <c r="G222" t="str">
-        <v>bữa tối</v>
+        <v>câu hỏi</v>
       </c>
       <c r="H222" t="str">
-        <v>16. Đồ ăn &amp; Thức uống</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B223">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C223" t="str">
-        <v>我晚上六点半下班</v>
+        <v>我叫李文</v>
       </c>
       <c r="D223" t="str">
-        <v>晚上</v>
+        <v>我</v>
       </c>
       <c r="E223" t="str">
-        <v>Danh từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F223" t="str">
-        <v>wǎnshang</v>
+        <v>wǒ</v>
       </c>
       <c r="G223" t="str">
-        <v>đêm</v>
+        <v>TÔI</v>
       </c>
       <c r="H223" t="str">
-        <v>10. Thời gian</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B224">
         <v>3</v>
@@ -6225,260 +6225,257 @@
         <v>我是中国人</v>
       </c>
       <c r="D224" t="str">
-        <v>喂</v>
+        <v>我们</v>
       </c>
       <c r="E224" t="str">
-        <v>Thán từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F224" t="str">
-        <v>wèi</v>
+        <v>wǒmen</v>
       </c>
       <c r="G224" t="str">
-        <v>Xin chào</v>
+        <v>chúng ta</v>
       </c>
       <c r="H224" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B225">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C225" t="str">
-        <v>我读大学了</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D225" t="str">
-        <v>问</v>
+        <v>五</v>
       </c>
       <c r="E225" t="str">
-        <v>Động từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F225" t="str">
-        <v>wèn</v>
+        <v>wǔ</v>
       </c>
       <c r="G225" t="str">
-        <v>hỏi</v>
+        <v>năm</v>
       </c>
       <c r="H225" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B226">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C226" t="str">
-        <v>请给我一杯茶</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D226" t="str">
-        <v>问题</v>
+        <v>午饭</v>
       </c>
       <c r="E226" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F226" t="str">
-        <v>wèntí</v>
+        <v>wǔfàn</v>
       </c>
       <c r="G226" t="str">
-        <v>câu hỏi</v>
+        <v>bữa trưa</v>
       </c>
       <c r="H226" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>16. Đồ ăn &amp; Thức uống</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C227" t="str">
-        <v>我叫李文</v>
+        <v>今天我休息</v>
       </c>
       <c r="D227" t="str">
-        <v>我</v>
+        <v>喜欢</v>
       </c>
       <c r="E227" t="str">
-        <v>Đại từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F227" t="str">
-        <v>wǒ</v>
+        <v>xǐhuan</v>
       </c>
       <c r="G227" t="str">
-        <v>TÔI</v>
+        <v>thích</v>
       </c>
       <c r="H227" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
-      </c>
-    </row>
-    <row r="228">
+        <v>3. Cảm xúc &amp; Thái độ</v>
+      </c>
+    </row>
+    <row r="228" xml:space="preserve">
       <c r="A228">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B228">
-        <v>3</v>
-      </c>
-      <c r="C228" t="str">
-        <v>我是中国人</v>
+        <v>8.12</v>
+      </c>
+      <c r="C228" t="str" xml:space="preserve">
+        <v xml:space="preserve">我明天上午在学校学习_x000d_
+昨天下雪了</v>
       </c>
       <c r="D228" t="str">
-        <v>我们</v>
+        <v>下</v>
       </c>
       <c r="E228" t="str">
-        <v>Đại từ</v>
+        <v>Danh từ, Động từ</v>
       </c>
       <c r="F228" t="str">
-        <v>wǒmen</v>
-      </c>
-      <c r="G228" t="str">
-        <v>chúng ta</v>
+        <v>xià</v>
+      </c>
+      <c r="G228" t="str" xml:space="preserve">
+        <v xml:space="preserve">danh từ - vị trí thấp (trên bảng xếp hạng)_x000d_
+động từ - rơi</v>
       </c>
       <c r="H228" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C229" t="str">
-        <v>我有两个孩子</v>
+        <v>今天我休息</v>
       </c>
       <c r="D229" t="str">
-        <v>五</v>
+        <v>下班</v>
       </c>
       <c r="E229" t="str">
-        <v>Số từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F229" t="str">
-        <v>wǔ</v>
+        <v>xiàbān</v>
       </c>
       <c r="G229" t="str">
-        <v>năm</v>
+        <v>tan ca làm việc</v>
       </c>
       <c r="H229" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B230">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C230" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D230" t="str">
-        <v>午饭</v>
+        <v>下课</v>
       </c>
       <c r="E230" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F230" t="str">
-        <v>wǔfàn</v>
+        <v>xiàkè</v>
       </c>
       <c r="G230" t="str">
-        <v>bữa trưa</v>
+        <v>Ra khỏi lớp học xong</v>
       </c>
       <c r="H230" t="str">
-        <v>16. Đồ ăn &amp; Thức uống</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B231">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C231" t="str">
-        <v>今天我休息</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D231" t="str">
-        <v>喜欢</v>
+        <v>下午</v>
       </c>
       <c r="E231" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F231" t="str">
-        <v>xǐhuan</v>
+        <v>xiàwǔ</v>
       </c>
       <c r="G231" t="str">
-        <v>thích</v>
+        <v>buổi chiều</v>
       </c>
       <c r="H231" t="str">
-        <v>3. Cảm xúc &amp; Thái độ</v>
-      </c>
-    </row>
-    <row r="232" xml:space="preserve">
+        <v>10. Thời gian</v>
+      </c>
+    </row>
+    <row r="232">
       <c r="A232">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B232">
-        <v>8.12</v>
-      </c>
-      <c r="C232" t="str" xml:space="preserve">
-        <v xml:space="preserve">我明天上午在学校学习_x000d_
-昨天下雪了</v>
+        <v>12</v>
+      </c>
+      <c r="C232" t="str">
+        <v>昨天下雪了</v>
       </c>
       <c r="D232" t="str">
-        <v>下</v>
-      </c>
-      <c r="E232" t="str">
-        <v>Danh từ, Động từ</v>
+        <v>下雨</v>
       </c>
       <c r="F232" t="str">
-        <v>xià</v>
-      </c>
-      <c r="G232" t="str" xml:space="preserve">
-        <v xml:space="preserve">danh từ - vị trí thấp (trên bảng xếp hạng)_x000d_
-động từ - rơi</v>
+        <v>xiàyǔ</v>
+      </c>
+      <c r="G232" t="str">
+        <v>mưa</v>
       </c>
       <c r="H232" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>15. Tự nhiên</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B233">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C233" t="str">
-        <v>今天我休息</v>
+        <v>请给我一杯茶</v>
       </c>
       <c r="D233" t="str">
-        <v>下班</v>
+        <v>先生</v>
       </c>
       <c r="E233" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F233" t="str">
-        <v>xiàbān</v>
+        <v>xiānsheng</v>
       </c>
       <c r="G233" t="str">
-        <v>tan ca làm việc</v>
+        <v>thưa quý ông</v>
       </c>
       <c r="H233" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B234">
         <v>7</v>
@@ -6487,91 +6484,95 @@
         <v>我晚上六点半下班</v>
       </c>
       <c r="D234" t="str">
-        <v>下课</v>
+        <v>现在</v>
       </c>
       <c r="E234" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F234" t="str">
-        <v>xiàkè</v>
+        <v>xiànzài</v>
       </c>
       <c r="G234" t="str">
-        <v>Ra khỏi lớp học xong</v>
+        <v>Hiện nay</v>
       </c>
       <c r="H234" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
-      </c>
-    </row>
-    <row r="235">
+        <v>10. Thời gian</v>
+      </c>
+    </row>
+    <row r="235" xml:space="preserve">
       <c r="A235">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B235">
-        <v>7</v>
-      </c>
-      <c r="C235" t="str">
-        <v>我晚上六点半下班</v>
+        <v>3.6</v>
+      </c>
+      <c r="C235" t="str" xml:space="preserve">
+        <v xml:space="preserve">我是中国人_x000d_
+你的手机号码是多少</v>
       </c>
       <c r="D235" t="str">
-        <v>下午</v>
+        <v>想</v>
       </c>
       <c r="E235" t="str">
-        <v>Danh từ</v>
+        <v>Động từ năng nguyện</v>
       </c>
       <c r="F235" t="str">
-        <v>xiàwǔ</v>
+        <v>xiǎng</v>
       </c>
       <c r="G235" t="str">
-        <v>buổi chiều</v>
+        <v>nghĩ</v>
       </c>
       <c r="H235" t="str">
-        <v>10. Thời gian</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B236">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C236" t="str">
-        <v>昨天下雪了</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D236" t="str">
-        <v>下雨</v>
+        <v>小</v>
+      </c>
+      <c r="E236" t="str">
+        <v>Tính từ</v>
       </c>
       <c r="F236" t="str">
-        <v>xiàyǔ</v>
+        <v>xiǎo</v>
       </c>
       <c r="G236" t="str">
-        <v>mưa</v>
+        <v>Bé nhỏ</v>
       </c>
       <c r="H236" t="str">
-        <v>15. Tự nhiên</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B237">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C237" t="str">
-        <v>请给我一杯茶</v>
+        <v>我读大学了</v>
       </c>
       <c r="D237" t="str">
-        <v>先生</v>
+        <v>小朋友</v>
       </c>
       <c r="E237" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F237" t="str">
-        <v>xiānsheng</v>
+        <v>xiǎopéngyou</v>
       </c>
       <c r="G237" t="str">
-        <v>thưa quý ông</v>
+        <v>đứa trẻ</v>
       </c>
       <c r="H237" t="str">
         <v>1. Con người &amp; Các mối quan hệ</v>
@@ -6579,268 +6580,267 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B238">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C238" t="str">
-        <v>我晚上六点半下班</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D238" t="str">
-        <v>现在</v>
+        <v>小时</v>
       </c>
       <c r="E238" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F238" t="str">
-        <v>xiànzài</v>
+        <v>xiǎoshí</v>
       </c>
       <c r="G238" t="str">
-        <v>Hiện nay</v>
+        <v>Giờ</v>
       </c>
       <c r="H238" t="str">
         <v>10. Thời gian</v>
       </c>
     </row>
-    <row r="239" xml:space="preserve">
+    <row r="239">
       <c r="A239">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B239">
-        <v>3.6</v>
-      </c>
-      <c r="C239" t="str" xml:space="preserve">
-        <v xml:space="preserve">我是中国人_x000d_
-你的手机号码是多少</v>
+        <v>14</v>
+      </c>
+      <c r="C239" t="str">
+        <v>我看了一个电影</v>
       </c>
       <c r="D239" t="str">
-        <v>想</v>
+        <v>小学</v>
       </c>
       <c r="E239" t="str">
-        <v>Động từ năng nguyện</v>
+        <v>Danh từ</v>
       </c>
       <c r="F239" t="str">
-        <v>xiǎng</v>
+        <v>xiǎoxué</v>
       </c>
       <c r="G239" t="str">
-        <v>nghĩ</v>
+        <v>trường tiểu học</v>
       </c>
       <c r="H239" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B240">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C240" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D240" t="str">
-        <v>小</v>
+        <v>小学生</v>
       </c>
       <c r="E240" t="str">
-        <v>Tính từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F240" t="str">
-        <v>xiǎo</v>
+        <v>xiǎoxuéshēng</v>
       </c>
       <c r="G240" t="str">
-        <v>Bé nhỏ</v>
+        <v>học sinh tiểu học</v>
       </c>
       <c r="H240" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B241">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C241" t="str">
-        <v>我读大学了</v>
+        <v>你的手机号码是多少</v>
       </c>
       <c r="D241" t="str">
-        <v>小朋友</v>
+        <v>些</v>
       </c>
       <c r="E241" t="str">
-        <v>Danh từ</v>
+        <v>Lượng từ</v>
       </c>
       <c r="F241" t="str">
-        <v>xiǎopéngyou</v>
+        <v>xiē</v>
       </c>
       <c r="G241" t="str">
-        <v>đứa trẻ</v>
+        <v>một số</v>
       </c>
       <c r="H241" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B242">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C242" t="str">
-        <v>大兴机场见！</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D242" t="str">
-        <v>小时</v>
+        <v>写</v>
       </c>
       <c r="E242" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F242" t="str">
-        <v>xiǎoshí</v>
+        <v>xiě</v>
       </c>
       <c r="G242" t="str">
-        <v>Giờ</v>
+        <v>Viết</v>
       </c>
       <c r="H242" t="str">
-        <v>10. Thời gian</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B243">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C243" t="str">
-        <v>我看了一个电影</v>
+        <v>AI 小语，你好！</v>
       </c>
       <c r="D243" t="str">
-        <v>小学</v>
+        <v>谢谢</v>
       </c>
       <c r="E243" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F243" t="str">
-        <v>xiǎoxué</v>
+        <v>xièxie</v>
       </c>
       <c r="G243" t="str">
-        <v>trường tiểu học</v>
+        <v>Cảm ơn</v>
       </c>
       <c r="H243" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B244">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C244" t="str">
-        <v>我看了一个电影</v>
+        <v>今天我休息</v>
       </c>
       <c r="D244" t="str">
-        <v>小学生</v>
+        <v>新</v>
       </c>
       <c r="E244" t="str">
-        <v>Danh từ</v>
+        <v>Tính từ</v>
       </c>
       <c r="F244" t="str">
-        <v>xiǎoxuéshēng</v>
+        <v>xīn</v>
       </c>
       <c r="G244" t="str">
-        <v>học sinh tiểu học</v>
+        <v>mới</v>
       </c>
       <c r="H244" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C245" t="str">
-        <v>你的手机号码是多少</v>
+        <v>今天我休息</v>
       </c>
       <c r="D245" t="str">
-        <v>些</v>
+        <v>星期</v>
       </c>
       <c r="E245" t="str">
-        <v>Lượng từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F245" t="str">
-        <v>xiē</v>
+        <v>xīngqī</v>
       </c>
       <c r="G245" t="str">
-        <v>một số</v>
+        <v>Tuần</v>
       </c>
       <c r="H245" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B246">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C246" t="str">
-        <v>我看了一个电影</v>
+        <v>今天我休息</v>
       </c>
       <c r="D246" t="str">
-        <v>写</v>
+        <v>星期日</v>
       </c>
       <c r="E246" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F246" t="str">
-        <v>xiě</v>
+        <v>xīngqīrì</v>
       </c>
       <c r="G246" t="str">
-        <v>Viết</v>
+        <v>Chủ nhật</v>
       </c>
       <c r="H246" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B247">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C247" t="str">
-        <v>AI 小语，你好！</v>
+        <v>今天我休息</v>
       </c>
       <c r="D247" t="str">
-        <v>谢谢</v>
+        <v>星期天</v>
       </c>
       <c r="E247" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F247" t="str">
-        <v>xièxie</v>
+        <v>xīngqītiān</v>
       </c>
       <c r="G247" t="str">
-        <v>Cảm ơn</v>
+        <v>Chủ nhật</v>
       </c>
       <c r="H247" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B248">
         <v>5</v>
@@ -6849,356 +6849,356 @@
         <v>今天我休息</v>
       </c>
       <c r="D248" t="str">
-        <v>新</v>
+        <v>休息</v>
       </c>
       <c r="E248" t="str">
-        <v>Tính từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F248" t="str">
-        <v>xīn</v>
+        <v>xiūxi</v>
       </c>
       <c r="G248" t="str">
-        <v>mới</v>
+        <v>nghỉ ngơi</v>
       </c>
       <c r="H248" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B249">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C249" t="str">
-        <v>今天我休息</v>
+        <v>我读大学了</v>
       </c>
       <c r="D249" t="str">
-        <v>星期</v>
+        <v>学</v>
       </c>
       <c r="E249" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F249" t="str">
-        <v>xīngqī</v>
+        <v>xué</v>
       </c>
       <c r="G249" t="str">
-        <v>Tuần</v>
+        <v>học</v>
       </c>
       <c r="H249" t="str">
-        <v>10. Thời gian</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B250">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C250" t="str">
-        <v>今天我休息</v>
+        <v>AI 小语，你好！</v>
       </c>
       <c r="D250" t="str">
-        <v>星期日</v>
+        <v>学生</v>
       </c>
       <c r="E250" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F250" t="str">
-        <v>xīngqīrì</v>
+        <v>xuésheng</v>
       </c>
       <c r="G250" t="str">
-        <v>Chủ nhật</v>
+        <v>học sinh</v>
       </c>
       <c r="H250" t="str">
-        <v>10. Thời gian</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B251">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C251" t="str">
-        <v>今天我休息</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D251" t="str">
-        <v>星期天</v>
+        <v>学习</v>
       </c>
       <c r="E251" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F251" t="str">
-        <v>xīngqītiān</v>
+        <v>xuéxí</v>
       </c>
       <c r="G251" t="str">
-        <v>Chủ nhật</v>
+        <v>học</v>
       </c>
       <c r="H251" t="str">
-        <v>10. Thời gian</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B252">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C252" t="str">
-        <v>今天我休息</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D252" t="str">
-        <v>休息</v>
+        <v>学校</v>
       </c>
       <c r="E252" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F252" t="str">
-        <v>xiūxi</v>
+        <v>xuéxiào</v>
       </c>
       <c r="G252" t="str">
-        <v>nghỉ ngơi</v>
+        <v>Trường học</v>
       </c>
       <c r="H252" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B253">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C253" t="str">
-        <v>我读大学了</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D253" t="str">
-        <v>学</v>
+        <v>雪</v>
       </c>
       <c r="E253" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F253" t="str">
-        <v>xué</v>
+        <v>xuě</v>
       </c>
       <c r="G253" t="str">
-        <v>học</v>
+        <v>Tuyết</v>
       </c>
       <c r="H253" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>15. Tự nhiên</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B254">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C254" t="str">
-        <v>AI 小语，你好！</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D254" t="str">
-        <v>学生</v>
+        <v>药</v>
       </c>
       <c r="E254" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F254" t="str">
-        <v>xuésheng</v>
+        <v>yào</v>
       </c>
       <c r="G254" t="str">
-        <v>học sinh</v>
+        <v>thuốc</v>
       </c>
       <c r="H254" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
-      </c>
-    </row>
-    <row r="255">
+        <v>2. Cơ thể &amp; Sức khỏe</v>
+      </c>
+    </row>
+    <row r="255" xml:space="preserve">
       <c r="A255">
-        <v>254</v>
-      </c>
-      <c r="B255">
-        <v>9</v>
-      </c>
-      <c r="C255" t="str">
-        <v>我明天上午在学校学习</v>
-      </c>
-      <c r="D255" t="str">
-        <v>学习</v>
-      </c>
-      <c r="E255" t="str">
-        <v>Động từ</v>
-      </c>
-      <c r="F255" t="str">
-        <v>xuéxí</v>
-      </c>
-      <c r="G255" t="str">
-        <v>học</v>
-      </c>
-      <c r="H255" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256">
-        <v>255</v>
-      </c>
-      <c r="B256">
-        <v>8</v>
-      </c>
-      <c r="C256" t="str">
-        <v>我明天上午在学校学习</v>
-      </c>
-      <c r="D256" t="str">
-        <v>学校</v>
-      </c>
-      <c r="E256" t="str">
-        <v>Danh từ</v>
-      </c>
-      <c r="F256" t="str">
-        <v>xuéxiào</v>
-      </c>
-      <c r="G256" t="str">
-        <v>Trường học</v>
-      </c>
-      <c r="H256" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257">
-        <v>256</v>
-      </c>
-      <c r="B257">
-        <v>12</v>
-      </c>
-      <c r="C257" t="str">
-        <v>昨天下雪了</v>
-      </c>
-      <c r="D257" t="str">
-        <v>雪</v>
-      </c>
-      <c r="E257" t="str">
-        <v>Danh từ</v>
-      </c>
-      <c r="F257" t="str">
-        <v>xuě</v>
-      </c>
-      <c r="G257" t="str">
-        <v>Tuyết</v>
-      </c>
-      <c r="H257" t="str">
-        <v>15. Tự nhiên</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258">
-        <v>257</v>
-      </c>
-      <c r="B258">
-        <v>12</v>
-      </c>
-      <c r="C258" t="str">
-        <v>昨天下雪了</v>
-      </c>
-      <c r="D258" t="str">
-        <v>药</v>
-      </c>
-      <c r="E258" t="str">
-        <v>Danh từ</v>
-      </c>
-      <c r="F258" t="str">
-        <v>yào</v>
-      </c>
-      <c r="G258" t="str">
-        <v>thuốc</v>
-      </c>
-      <c r="H258" t="str">
-        <v>2. Cơ thể &amp; Sức khỏe</v>
-      </c>
-    </row>
-    <row r="259" xml:space="preserve">
-      <c r="A259">
         <v>258</v>
       </c>
-      <c r="B259" t="str">
+      <c r="B255" t="str">
         <v>11,13,15</v>
       </c>
-      <c r="C259" t="str" xml:space="preserve">
+      <c r="C255" t="str" xml:space="preserve">
         <v xml:space="preserve">大兴机场见！_x000d_
 请给我一杯茶_x000d_
 我读大学了</v>
       </c>
+      <c r="D255" t="str">
+        <v>要</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Động từ năng nguyện</v>
+      </c>
+      <c r="F255" t="str">
+        <v>yào</v>
+      </c>
+      <c r="G255" t="str">
+        <v>muốn; cần, lấy</v>
+      </c>
+      <c r="H255" t="str">
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>259</v>
+      </c>
+      <c r="B256">
+        <v>2</v>
+      </c>
+      <c r="C256" t="str">
+        <v>我叫李文</v>
+      </c>
+      <c r="D256" t="str">
+        <v>也</v>
+      </c>
+      <c r="E256" t="str">
+        <v>Phó từ</v>
+      </c>
+      <c r="F256" t="str">
+        <v>yě</v>
+      </c>
+      <c r="G256" t="str">
+        <v>Mà còn</v>
+      </c>
+      <c r="H256" t="str">
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>260</v>
+      </c>
+      <c r="B257">
+        <v>4</v>
+      </c>
+      <c r="C257" t="str">
+        <v>我有两个孩子</v>
+      </c>
+      <c r="D257" t="str">
+        <v>一</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Số từ</v>
+      </c>
+      <c r="F257" t="str">
+        <v>yī</v>
+      </c>
+      <c r="G257" t="str">
+        <v>một</v>
+      </c>
+      <c r="H257" t="str">
+        <v>13. Số lượng &amp; Đo lường</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>261</v>
+      </c>
+      <c r="B258">
+        <v>13</v>
+      </c>
+      <c r="C258" t="str">
+        <v>请给我一杯茶</v>
+      </c>
+      <c r="D258" t="str">
+        <v>一半</v>
+      </c>
+      <c r="E258" t="str">
+        <v>Số từ</v>
+      </c>
+      <c r="F258" t="str">
+        <v>yíbàn</v>
+      </c>
+      <c r="G258" t="str">
+        <v>một nửa</v>
+      </c>
+      <c r="H258" t="str">
+        <v>13. Số lượng &amp; Đo lường</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>262</v>
+      </c>
+      <c r="B259">
+        <v>13</v>
+      </c>
+      <c r="C259" t="str">
+        <v>请给我一杯茶</v>
+      </c>
       <c r="D259" t="str">
-        <v>要</v>
+        <v>一下</v>
       </c>
       <c r="E259" t="str">
-        <v>Động từ năng nguyện</v>
+        <v>Lượng từ, Số từ</v>
       </c>
       <c r="F259" t="str">
-        <v>yào</v>
+        <v>yíxià</v>
       </c>
       <c r="G259" t="str">
-        <v>muốn; cần, lấy</v>
+        <v>một lần</v>
       </c>
       <c r="H259" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B260">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C260" t="str">
-        <v>我叫李文</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D260" t="str">
-        <v>也</v>
+        <v>一点儿</v>
       </c>
       <c r="E260" t="str">
-        <v>Phó từ</v>
+        <v>Số từ</v>
       </c>
       <c r="F260" t="str">
-        <v>yě</v>
+        <v>yìdiǎnr</v>
       </c>
       <c r="G260" t="str">
-        <v>Mà còn</v>
+        <v>một chút</v>
       </c>
       <c r="H260" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B261">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C261" t="str">
-        <v>我有两个孩子</v>
+        <v>今天我休息</v>
       </c>
       <c r="D261" t="str">
-        <v>一</v>
+        <v>一些</v>
       </c>
       <c r="E261" t="str">
         <v>Số từ</v>
       </c>
       <c r="F261" t="str">
-        <v>yī</v>
+        <v>yìxiē</v>
       </c>
       <c r="G261" t="str">
-        <v>một</v>
+        <v>Một số</v>
       </c>
       <c r="H261" t="str">
         <v>13. Số lượng &amp; Đo lường</v>
@@ -7206,129 +7206,129 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B262">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C262" t="str">
-        <v>请给我一杯茶</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D262" t="str">
-        <v>一半</v>
+        <v>衣服</v>
       </c>
       <c r="E262" t="str">
-        <v>Số từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F262" t="str">
-        <v>yíbàn</v>
+        <v>yīfu</v>
       </c>
       <c r="G262" t="str">
-        <v>một nửa</v>
+        <v>quần áo</v>
       </c>
       <c r="H262" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B263">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C263" t="str">
-        <v>请给我一杯茶</v>
+        <v>我读大学了</v>
       </c>
       <c r="D263" t="str">
-        <v>一下</v>
+        <v>医</v>
       </c>
       <c r="E263" t="str">
-        <v>Lượng từ, Số từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F263" t="str">
-        <v>yíxià</v>
+        <v>yī</v>
       </c>
       <c r="G263" t="str">
-        <v>một lần</v>
+        <v>y học</v>
       </c>
       <c r="H263" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B264">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C264" t="str">
-        <v>昨天下雪了</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D264" t="str">
-        <v>一点儿</v>
+        <v>医生</v>
       </c>
       <c r="E264" t="str">
-        <v>Số từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F264" t="str">
-        <v>yìdiǎnr</v>
+        <v>yīshēng</v>
       </c>
       <c r="G264" t="str">
-        <v>một chút</v>
+        <v>bác sĩ</v>
       </c>
       <c r="H264" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B265">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C265" t="str">
-        <v>今天我休息</v>
+        <v>我晚上六点半下班</v>
       </c>
       <c r="D265" t="str">
-        <v>一些</v>
+        <v>医院</v>
       </c>
       <c r="E265" t="str">
-        <v>Số từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F265" t="str">
-        <v>yìxiē</v>
+        <v>yīyuàn</v>
       </c>
       <c r="G265" t="str">
-        <v>Một số</v>
+        <v>Bệnh viện</v>
       </c>
       <c r="H265" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B266">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C266" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D266" t="str">
-        <v>衣服</v>
+        <v>椅子</v>
       </c>
       <c r="E266" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F266" t="str">
-        <v>yīfu</v>
+        <v>yǐzi</v>
       </c>
       <c r="G266" t="str">
-        <v>quần áo</v>
+        <v>Ghế</v>
       </c>
       <c r="H266" t="str">
         <v>6. Đồ vật &amp; Công cụ</v>
@@ -7336,366 +7336,366 @@
     </row>
     <row r="267">
       <c r="A267">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B267">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C267" t="str">
-        <v>我读大学了</v>
+        <v>我有两个孩子</v>
       </c>
       <c r="D267" t="str">
-        <v>医</v>
+        <v>有</v>
       </c>
       <c r="E267" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F267" t="str">
-        <v>yī</v>
+        <v>yǒu</v>
       </c>
       <c r="G267" t="str">
-        <v>y học</v>
+        <v>có</v>
       </c>
       <c r="H267" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B268">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C268" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D268" t="str">
-        <v>医生</v>
+        <v>有的</v>
       </c>
       <c r="E268" t="str">
-        <v>Danh từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F268" t="str">
-        <v>yīshēng</v>
+        <v>yǒude</v>
       </c>
       <c r="G268" t="str">
-        <v>bác sĩ</v>
+        <v>một số</v>
       </c>
       <c r="H268" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B269">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C269" t="str">
-        <v>我晚上六点半下班</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D269" t="str">
-        <v>医院</v>
+        <v>有点儿</v>
       </c>
       <c r="E269" t="str">
-        <v>Danh từ</v>
+        <v>Phó từ</v>
       </c>
       <c r="F269" t="str">
-        <v>yīyuàn</v>
+        <v>yǒudiǎnr</v>
       </c>
       <c r="G269" t="str">
-        <v>Bệnh viện</v>
+        <v>có chút hơi...</v>
       </c>
       <c r="H269" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B270">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C270" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D270" t="str">
-        <v>椅子</v>
+        <v>有些</v>
       </c>
       <c r="E270" t="str">
-        <v>Danh từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F270" t="str">
-        <v>yǐzi</v>
+        <v>yǒuxiē</v>
       </c>
       <c r="G270" t="str">
-        <v>Ghế</v>
+        <v>một số</v>
       </c>
       <c r="H270" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B271">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C271" t="str">
-        <v>我有两个孩子</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D271" t="str">
-        <v>有</v>
+        <v>雨</v>
       </c>
       <c r="E271" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F271" t="str">
-        <v>yǒu</v>
+        <v>yǔ</v>
       </c>
       <c r="G271" t="str">
-        <v>có</v>
+        <v>cơn mưa</v>
       </c>
       <c r="H271" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>15. Tự nhiên</v>
       </c>
     </row>
     <row r="272">
       <c r="A272">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B272">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C272" t="str">
-        <v>我看了一个电影</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D272" t="str">
-        <v>有的</v>
+        <v>元</v>
       </c>
       <c r="E272" t="str">
-        <v>Đại từ</v>
+        <v>Lượng từ</v>
       </c>
       <c r="F272" t="str">
-        <v>yǒude</v>
+        <v>yuán</v>
       </c>
       <c r="G272" t="str">
-        <v>một số</v>
+        <v>đơn vị tiền Nhân Dân Tệ</v>
       </c>
       <c r="H272" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="273">
       <c r="A273">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B273">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C273" t="str">
-        <v>昨天下雪了</v>
+        <v>今天我休息</v>
       </c>
       <c r="D273" t="str">
-        <v>有点儿</v>
+        <v>月</v>
       </c>
       <c r="E273" t="str">
+        <v>Danh từ</v>
+      </c>
+      <c r="F273" t="str">
+        <v>yuè</v>
+      </c>
+      <c r="G273" t="str">
+        <v>mặt trăng</v>
+      </c>
+      <c r="H273" t="str">
+        <v>10. Thời gian</v>
+      </c>
+    </row>
+    <row r="274" xml:space="preserve">
+      <c r="A274">
+        <v>277</v>
+      </c>
+      <c r="B274">
+        <v>12.13</v>
+      </c>
+      <c r="C274" t="str" xml:space="preserve">
+        <v xml:space="preserve">请给我一杯茶_x000d_
+昨天下雪了</v>
+      </c>
+      <c r="D274" t="str">
+        <v>再</v>
+      </c>
+      <c r="E274" t="str">
         <v>Phó từ</v>
       </c>
-      <c r="F273" t="str">
-        <v>yǒudiǎnr</v>
-      </c>
-      <c r="G273" t="str">
-        <v>có chút hơi...</v>
-      </c>
-      <c r="H273" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274">
-        <v>273</v>
-      </c>
-      <c r="B274">
-        <v>14</v>
-      </c>
-      <c r="C274" t="str">
-        <v>我看了一个电影</v>
-      </c>
-      <c r="D274" t="str">
-        <v>有些</v>
-      </c>
-      <c r="E274" t="str">
-        <v>Đại từ</v>
-      </c>
       <c r="F274" t="str">
-        <v>yǒuxiē</v>
+        <v>zài</v>
       </c>
       <c r="G274" t="str">
-        <v>một số</v>
+        <v>Lại</v>
       </c>
       <c r="H274" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B275">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C275" t="str">
-        <v>昨天下雪了</v>
+        <v>AI 小语，你好！</v>
       </c>
       <c r="D275" t="str">
-        <v>雨</v>
+        <v>再见</v>
       </c>
       <c r="E275" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F275" t="str">
-        <v>yǔ</v>
+        <v>zàijiàn</v>
       </c>
       <c r="G275" t="str">
-        <v>cơn mưa</v>
+        <v>tạm biệt</v>
       </c>
       <c r="H275" t="str">
-        <v>15. Tự nhiên</v>
-      </c>
-    </row>
-    <row r="276">
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+      </c>
+    </row>
+    <row r="276" xml:space="preserve">
       <c r="A276">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B276">
-        <v>10</v>
-      </c>
-      <c r="C276" t="str">
-        <v>这儿的苹果真便宜</v>
-      </c>
-      <c r="D276" t="str">
-        <v>元</v>
-      </c>
-      <c r="E276" t="str">
-        <v>Lượng từ</v>
-      </c>
-      <c r="F276" t="str">
-        <v>yuán</v>
-      </c>
-      <c r="G276" t="str">
-        <v>đơn vị tiền Nhân Dân Tệ</v>
-      </c>
-      <c r="H276" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277">
-        <v>276</v>
-      </c>
-      <c r="B277">
-        <v>5</v>
-      </c>
-      <c r="C277" t="str">
-        <v>今天我休息</v>
-      </c>
-      <c r="D277" t="str">
-        <v>月</v>
-      </c>
-      <c r="E277" t="str">
-        <v>Danh từ</v>
-      </c>
-      <c r="F277" t="str">
-        <v>yuè</v>
-      </c>
-      <c r="G277" t="str">
-        <v>mặt trăng</v>
-      </c>
-      <c r="H277" t="str">
-        <v>10. Thời gian</v>
-      </c>
-    </row>
-    <row r="278" xml:space="preserve">
-      <c r="A278">
-        <v>277</v>
-      </c>
-      <c r="B278">
-        <v>12.13</v>
-      </c>
-      <c r="C278" t="str" xml:space="preserve">
-        <v xml:space="preserve">请给我一杯茶_x000d_
-昨天下雪了</v>
-      </c>
-      <c r="D278" t="str">
-        <v>再</v>
-      </c>
-      <c r="E278" t="str">
-        <v>Phó từ</v>
-      </c>
-      <c r="F278" t="str">
-        <v>zài</v>
-      </c>
-      <c r="G278" t="str">
-        <v>Lại</v>
-      </c>
-      <c r="H278" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279">
-        <v>278</v>
-      </c>
-      <c r="B279">
-        <v>1</v>
-      </c>
-      <c r="C279" t="str">
-        <v>AI 小语，你好！</v>
-      </c>
-      <c r="D279" t="str">
-        <v>再见</v>
-      </c>
-      <c r="E279" t="str">
-        <v>Động từ</v>
-      </c>
-      <c r="F279" t="str">
-        <v>zàijiàn</v>
-      </c>
-      <c r="G279" t="str">
-        <v>tạm biệt</v>
-      </c>
-      <c r="H279" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
-      </c>
-    </row>
-    <row r="280" xml:space="preserve">
-      <c r="A280">
-        <v>279</v>
-      </c>
-      <c r="B280">
         <v>40762</v>
       </c>
-      <c r="C280" t="str" xml:space="preserve">
+      <c r="C276" t="str" xml:space="preserve">
         <v xml:space="preserve">我晚上六点半下班_x000d_
 我明天上午在学校学习_x000d_
 我读大学了</v>
       </c>
+      <c r="D276" t="str">
+        <v>在</v>
+      </c>
+      <c r="E276" t="str">
+        <v>Động từ, Phó từ</v>
+      </c>
+      <c r="F276" t="str">
+        <v>zài</v>
+      </c>
+      <c r="G276" t="str">
+        <v>hiện hữu, đang diễn ra</v>
+      </c>
+      <c r="H276" t="str">
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>280</v>
+      </c>
+      <c r="B277">
+        <v>15</v>
+      </c>
+      <c r="C277" t="str">
+        <v>大兴机场见！</v>
+      </c>
+      <c r="D277" t="str">
+        <v>早</v>
+      </c>
+      <c r="E277" t="str">
+        <v>Tính từ</v>
+      </c>
+      <c r="F277" t="str">
+        <v>zǎo</v>
+      </c>
+      <c r="G277" t="str">
+        <v>sớm</v>
+      </c>
+      <c r="H277" t="str">
+        <v>10. Thời gian</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>281</v>
+      </c>
+      <c r="B278">
+        <v>13</v>
+      </c>
+      <c r="C278" t="str">
+        <v>请给我一杯茶</v>
+      </c>
+      <c r="D278" t="str">
+        <v>早饭</v>
+      </c>
+      <c r="E278" t="str">
+        <v>Danh từ</v>
+      </c>
+      <c r="F278" t="str">
+        <v>zǎofàn</v>
+      </c>
+      <c r="G278" t="str">
+        <v>bữa sáng</v>
+      </c>
+      <c r="H278" t="str">
+        <v>16. Đồ ăn &amp; Thức uống</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>282</v>
+      </c>
+      <c r="B279">
+        <v>7</v>
+      </c>
+      <c r="C279" t="str">
+        <v>我晚上六点半下班</v>
+      </c>
+      <c r="D279" t="str">
+        <v>早上</v>
+      </c>
+      <c r="E279" t="str">
+        <v>Danh từ</v>
+      </c>
+      <c r="F279" t="str">
+        <v>zǎoshang</v>
+      </c>
+      <c r="G279" t="str">
+        <v>Buổi sáng</v>
+      </c>
+      <c r="H279" t="str">
+        <v>15. Tự nhiên</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>283</v>
+      </c>
+      <c r="B280">
+        <v>6</v>
+      </c>
+      <c r="C280" t="str">
+        <v>你的手机号码是多少</v>
+      </c>
       <c r="D280" t="str">
-        <v>在</v>
+        <v>怎么</v>
       </c>
       <c r="E280" t="str">
-        <v>Động từ, Phó từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F280" t="str">
-        <v>zài</v>
+        <v>zěnme</v>
       </c>
       <c r="G280" t="str">
-        <v>hiện hữu, đang diễn ra</v>
+        <v>Làm sao</v>
       </c>
       <c r="H280" t="str">
         <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
@@ -7703,163 +7703,151 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B281">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C281" t="str">
-        <v>大兴机场见！</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D281" t="str">
-        <v>早</v>
+        <v>怎么样</v>
       </c>
       <c r="E281" t="str">
-        <v>Tính từ</v>
+        <v>Đại từ</v>
       </c>
       <c r="F281" t="str">
-        <v>zǎo</v>
+        <v>zěnmeyàng</v>
       </c>
       <c r="G281" t="str">
-        <v>sớm</v>
+        <v>Thế nào?</v>
       </c>
       <c r="H281" t="str">
-        <v>10. Thời gian</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="282">
       <c r="A282">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B282">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C282" t="str">
-        <v>请给我一杯茶</v>
+        <v>我读大学了</v>
       </c>
       <c r="D282" t="str">
-        <v>早饭</v>
+        <v>找</v>
       </c>
       <c r="E282" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F282" t="str">
-        <v>zǎofàn</v>
+        <v>zhǎo</v>
       </c>
       <c r="G282" t="str">
-        <v>bữa sáng</v>
+        <v>cố gắng tìm</v>
       </c>
       <c r="H282" t="str">
-        <v>16. Đồ ăn &amp; Thức uống</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="283">
       <c r="A283">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B283">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C283" t="str">
-        <v>我晚上六点半下班</v>
+        <v>我是中国人</v>
       </c>
       <c r="D283" t="str">
-        <v>早上</v>
-      </c>
-      <c r="E283" t="str">
-        <v>Danh từ</v>
+        <v>中国</v>
       </c>
       <c r="F283" t="str">
-        <v>zǎoshang</v>
+        <v xml:space="preserve">Zhōngguó </v>
       </c>
       <c r="G283" t="str">
-        <v>Buổi sáng</v>
+        <v>Trung Quốc</v>
       </c>
       <c r="H283" t="str">
-        <v>15. Tự nhiên</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B284">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C284" t="str">
-        <v>你的手机号码是多少</v>
+        <v>我是中国人</v>
       </c>
       <c r="D284" t="str">
-        <v>怎么</v>
-      </c>
-      <c r="E284" t="str">
-        <v>Đại từ</v>
+        <v>法国</v>
       </c>
       <c r="F284" t="str">
-        <v>zěnme</v>
+        <v>Fǎguó</v>
       </c>
       <c r="G284" t="str">
-        <v>Làm sao</v>
+        <v>Pháp</v>
       </c>
       <c r="H284" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="285">
       <c r="A285">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B285">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C285" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我是中国人</v>
       </c>
       <c r="D285" t="str">
-        <v>怎么样</v>
-      </c>
-      <c r="E285" t="str">
-        <v>Đại từ</v>
+        <v>泰国</v>
       </c>
       <c r="F285" t="str">
-        <v>zěnmeyàng</v>
+        <v>tàiguó</v>
       </c>
       <c r="G285" t="str">
-        <v>Thế nào?</v>
+        <v>Thái Lan</v>
       </c>
       <c r="H285" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="286">
       <c r="A286">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B286">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C286" t="str">
-        <v>我读大学了</v>
+        <v>我是中国人</v>
       </c>
       <c r="D286" t="str">
-        <v>找</v>
-      </c>
-      <c r="E286" t="str">
-        <v>Động từ</v>
+        <v>中文</v>
       </c>
       <c r="F286" t="str">
-        <v>zhǎo</v>
+        <v xml:space="preserve">zhōngwén </v>
       </c>
       <c r="G286" t="str">
-        <v>cố gắng tìm</v>
+        <v>Tiếng Trung</v>
       </c>
       <c r="H286" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="287">
       <c r="A287">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B287">
         <v>3</v>
@@ -7868,21 +7856,24 @@
         <v>我是中国人</v>
       </c>
       <c r="D287" t="str">
-        <v>中国</v>
+        <v>她</v>
+      </c>
+      <c r="E287" t="str">
+        <v>Đại từ</v>
       </c>
       <c r="F287" t="str">
-        <v xml:space="preserve">Zhōngguó </v>
+        <v xml:space="preserve">tā </v>
       </c>
       <c r="G287" t="str">
-        <v>Trung Quốc</v>
+        <v>cô ấy</v>
       </c>
       <c r="H287" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>1. Con người &amp; Các mối quan hệ</v>
       </c>
     </row>
     <row r="288">
       <c r="A288">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B288">
         <v>3</v>
@@ -7891,119 +7882,128 @@
         <v>我是中国人</v>
       </c>
       <c r="D288" t="str">
-        <v>法国</v>
+        <v>这</v>
+      </c>
+      <c r="E288" t="str">
+        <v>Đại từ</v>
       </c>
       <c r="F288" t="str">
-        <v>Fǎguó</v>
+        <v>zhè</v>
       </c>
       <c r="G288" t="str">
-        <v>Pháp</v>
+        <v>cái này</v>
       </c>
       <c r="H288" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="289">
       <c r="A289">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B289">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C289" t="str">
-        <v>我是中国人</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D289" t="str">
-        <v>泰国</v>
+        <v>这边</v>
+      </c>
+      <c r="E289" t="str">
+        <v>Đại từ</v>
       </c>
       <c r="F289" t="str">
-        <v>tàiguó</v>
+        <v>zhèbiān</v>
       </c>
       <c r="G289" t="str">
-        <v>Thái Lan</v>
+        <v>Theo cách này</v>
       </c>
       <c r="H289" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="290">
       <c r="A290">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B290">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C290" t="str">
-        <v>我是中国人</v>
+        <v>请给我一杯茶</v>
       </c>
       <c r="D290" t="str">
-        <v>中文</v>
+        <v>这个</v>
+      </c>
+      <c r="E290" t="str">
+        <v>Đại từ</v>
       </c>
       <c r="F290" t="str">
-        <v xml:space="preserve">zhōngwén </v>
+        <v>zhège</v>
       </c>
       <c r="G290" t="str">
-        <v>Tiếng Trung</v>
+        <v>cái này</v>
       </c>
       <c r="H290" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>9. Không gian &amp; Vị trí</v>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B291">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C291" t="str">
-        <v>我是中国人</v>
+        <v>昨天下雪了</v>
       </c>
       <c r="D291" t="str">
-        <v>她</v>
+        <v>这里</v>
       </c>
       <c r="E291" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F291" t="str">
-        <v xml:space="preserve">tā </v>
+        <v>zhèlǐ</v>
       </c>
       <c r="G291" t="str">
-        <v>cô ấy</v>
+        <v>đây</v>
       </c>
       <c r="H291" t="str">
-        <v>1. Con người &amp; Các mối quan hệ</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B292">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C292" t="str">
-        <v>我是中国人</v>
+        <v>这儿的苹果真便宜</v>
       </c>
       <c r="D292" t="str">
-        <v>这</v>
+        <v>这儿</v>
       </c>
       <c r="E292" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F292" t="str">
-        <v>zhè</v>
+        <v>zhèr</v>
       </c>
       <c r="G292" t="str">
-        <v>cái này</v>
+        <v>đây</v>
       </c>
       <c r="H292" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="293">
       <c r="A293">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B293">
         <v>10</v>
@@ -8012,276 +8012,270 @@
         <v>这儿的苹果真便宜</v>
       </c>
       <c r="D293" t="str">
-        <v>这边</v>
+        <v>这些</v>
       </c>
       <c r="E293" t="str">
         <v>Đại từ</v>
       </c>
       <c r="F293" t="str">
-        <v>zhèbiān</v>
+        <v>zhèxiē</v>
       </c>
       <c r="G293" t="str">
-        <v>Theo cách này</v>
+        <v>Những cái này</v>
       </c>
       <c r="H293" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
       </c>
     </row>
     <row r="294">
       <c r="A294">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B294">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C294" t="str">
-        <v>请给我一杯茶</v>
+        <v>今天我休息</v>
       </c>
       <c r="D294" t="str">
-        <v>这个</v>
+        <v>真</v>
       </c>
       <c r="E294" t="str">
-        <v>Đại từ</v>
+        <v>Phó từ</v>
       </c>
       <c r="F294" t="str">
-        <v>zhège</v>
+        <v>zhēn</v>
       </c>
       <c r="G294" t="str">
-        <v>cái này</v>
+        <v>thật, rất</v>
       </c>
       <c r="H294" t="str">
-        <v>9. Không gian &amp; Vị trí</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B295">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C295" t="str">
-        <v>昨天下雪了</v>
+        <v>我读大学了</v>
       </c>
       <c r="D295" t="str">
-        <v>这里</v>
+        <v>正在</v>
       </c>
       <c r="E295" t="str">
-        <v>Đại từ</v>
+        <v>Phó từ</v>
       </c>
       <c r="F295" t="str">
-        <v>zhèlǐ</v>
+        <v>zhèngzài</v>
       </c>
       <c r="G295" t="str">
-        <v>đây</v>
+        <v>Đang tiến hành</v>
       </c>
       <c r="H295" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>12. Miêu tả &amp; Đánh giá</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B296">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C296" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D296" t="str">
-        <v>这儿</v>
+        <v>只</v>
       </c>
       <c r="E296" t="str">
-        <v>Đại từ</v>
+        <v>Lượng từ</v>
       </c>
       <c r="F296" t="str">
-        <v>zhèr</v>
+        <v xml:space="preserve">zhī </v>
       </c>
       <c r="G296" t="str">
-        <v>đây</v>
+        <v>lượng từ dùng cho con vật</v>
       </c>
       <c r="H296" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>13. Số lượng &amp; Đo lường</v>
       </c>
     </row>
     <row r="297">
       <c r="A297">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B297">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C297" t="str">
-        <v>这儿的苹果真便宜</v>
+        <v>我读大学了</v>
       </c>
       <c r="D297" t="str">
-        <v>这些</v>
+        <v>知道</v>
       </c>
       <c r="E297" t="str">
-        <v>Đại từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F297" t="str">
-        <v>zhèxiē</v>
+        <v>zhīdào</v>
       </c>
       <c r="G297" t="str">
-        <v>Những cái này</v>
+        <v>biết, nhận ra</v>
       </c>
       <c r="H297" t="str">
-        <v>14. Công cụ ngữ pháp &amp; Cấu trúc</v>
+        <v>4. Tư duy &amp; Nhận thức</v>
       </c>
     </row>
     <row r="298">
       <c r="A298">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B298">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C298" t="str">
-        <v>今天我休息</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D298" t="str">
-        <v>真</v>
+        <v>中午</v>
       </c>
       <c r="E298" t="str">
-        <v>Phó từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F298" t="str">
-        <v>zhēn</v>
+        <v>zhōngwǔ</v>
       </c>
       <c r="G298" t="str">
-        <v>thật, rất</v>
+        <v>buổi trưa</v>
       </c>
       <c r="H298" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>10. Thời gian</v>
       </c>
     </row>
     <row r="299">
       <c r="A299">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B299">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C299" t="str">
-        <v>我读大学了</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D299" t="str">
-        <v>正在</v>
+        <v>中学</v>
       </c>
       <c r="E299" t="str">
-        <v>Phó từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F299" t="str">
-        <v>zhèngzài</v>
+        <v>zhōngxué</v>
       </c>
       <c r="G299" t="str">
-        <v>Đang tiến hành</v>
+        <v>Trường trung học cơ sở</v>
       </c>
       <c r="H299" t="str">
-        <v>12. Miêu tả &amp; Đánh giá</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B300">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C300" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D300" t="str">
-        <v>只</v>
+        <v>中学生</v>
       </c>
       <c r="E300" t="str">
-        <v>Lượng từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F300" t="str">
-        <v xml:space="preserve">zhī </v>
+        <v>zhōngxuéshēng</v>
       </c>
       <c r="G300" t="str">
-        <v>lượng từ dùng cho con vật</v>
+        <v>học sinh trung học</v>
       </c>
       <c r="H300" t="str">
-        <v>13. Số lượng &amp; Đo lường</v>
+        <v>11. Công việc &amp; Nghề nghiệp</v>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B301">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C301" t="str">
-        <v>我读大学了</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D301" t="str">
-        <v>知道</v>
+        <v>住</v>
       </c>
       <c r="E301" t="str">
         <v>Động từ</v>
       </c>
       <c r="F301" t="str">
-        <v>zhīdào</v>
+        <v>zhù</v>
       </c>
       <c r="G301" t="str">
-        <v>biết, nhận ra</v>
+        <v>sống</v>
       </c>
       <c r="H301" t="str">
-        <v>4. Tư duy &amp; Nhận thức</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B302">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C302" t="str">
-        <v>我看了一个电影</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D302" t="str">
-        <v>中午</v>
-      </c>
-      <c r="E302" t="str">
-        <v>Danh từ</v>
+        <v>西安</v>
       </c>
       <c r="F302" t="str">
-        <v>zhōngwǔ</v>
+        <v>Xī'ān</v>
       </c>
       <c r="G302" t="str">
-        <v>buổi trưa</v>
+        <v>Tây An</v>
       </c>
       <c r="H302" t="str">
-        <v>10. Thời gian</v>
+        <v>7. Địa điểm &amp; Nơi chốn</v>
       </c>
     </row>
     <row r="303">
       <c r="A303">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B303">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C303" t="str">
-        <v>我看了一个电影</v>
+        <v>大兴机场见！</v>
       </c>
       <c r="D303" t="str">
-        <v>中学</v>
-      </c>
-      <c r="E303" t="str">
-        <v>Danh từ</v>
+        <v>北京</v>
       </c>
       <c r="F303" t="str">
-        <v>zhōngxué</v>
+        <v>Běijīng</v>
       </c>
       <c r="G303" t="str">
-        <v>Trường trung học cơ sở</v>
+        <v>Bắc Kinh</v>
       </c>
       <c r="H303" t="str">
         <v>7. Địa điểm &amp; Nơi chốn</v>
@@ -8289,311 +8283,213 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B304">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C304" t="str">
-        <v>我看了一个电影</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D304" t="str">
-        <v>中学生</v>
+        <v>桌子</v>
       </c>
       <c r="E304" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F304" t="str">
-        <v>zhōngxuéshēng</v>
+        <v>zhuōzi</v>
       </c>
       <c r="G304" t="str">
-        <v>học sinh trung học</v>
+        <v>bàn</v>
       </c>
       <c r="H304" t="str">
-        <v>11. Công việc &amp; Nghề nghiệp</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B305">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C305" t="str">
-        <v>大兴机场见！</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D305" t="str">
-        <v>住</v>
+        <v>字</v>
       </c>
       <c r="E305" t="str">
-        <v>Động từ</v>
+        <v>Danh từ</v>
       </c>
       <c r="F305" t="str">
-        <v>zhù</v>
+        <v>zì</v>
       </c>
       <c r="G305" t="str">
-        <v>sống</v>
+        <v>chữ cái</v>
       </c>
       <c r="H305" t="str">
-        <v>5. Đời sống sinh hoạt</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="306">
       <c r="A306">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B306">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C306" t="str">
-        <v>大兴机场见！</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D306" t="str">
-        <v>西安</v>
+        <v>汉语</v>
+      </c>
+      <c r="E306" t="str">
+        <v>Danh từ</v>
       </c>
       <c r="F306" t="str">
-        <v>Xī'ān</v>
+        <v>hànyǔ</v>
       </c>
       <c r="G306" t="str">
-        <v>Tây An</v>
+        <v>Tiếng Trung</v>
       </c>
       <c r="H306" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="307">
       <c r="A307">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B307">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C307" t="str">
-        <v>大兴机场见！</v>
+        <v>我看了一个电影</v>
       </c>
       <c r="D307" t="str">
-        <v>北京</v>
+        <v>汉字</v>
+      </c>
+      <c r="E307" t="str">
+        <v>Danh từ</v>
       </c>
       <c r="F307" t="str">
-        <v>Běijīng</v>
+        <v>hànzì</v>
       </c>
       <c r="G307" t="str">
-        <v>Bắc Kinh</v>
+        <v>Hán tự, chữ cái tiếng Trung</v>
       </c>
       <c r="H307" t="str">
-        <v>7. Địa điểm &amp; Nơi chốn</v>
+        <v>6. Đồ vật &amp; Công cụ</v>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B308">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C308" t="str">
-        <v>我明天上午在学校学习</v>
+        <v>我读大学了</v>
       </c>
       <c r="D308" t="str">
-        <v>桌子</v>
+        <v>昨天</v>
       </c>
       <c r="E308" t="str">
         <v>Danh từ</v>
       </c>
       <c r="F308" t="str">
-        <v>zhuōzi</v>
+        <v>zuótiān</v>
       </c>
       <c r="G308" t="str">
-        <v>bàn</v>
+        <v>hôm qua</v>
       </c>
       <c r="H308" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
-      </c>
-    </row>
-    <row r="309">
+        <v>10. Thời gian</v>
+      </c>
+    </row>
+    <row r="309" xml:space="preserve">
       <c r="A309">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B309">
-        <v>14</v>
-      </c>
-      <c r="C309" t="str">
-        <v>我看了一个电影</v>
+        <v>6.13</v>
+      </c>
+      <c r="C309" t="str" xml:space="preserve">
+        <v xml:space="preserve">你的手机号码是多少_x000d_
+请给我一杯茶</v>
       </c>
       <c r="D309" t="str">
-        <v>字</v>
+        <v>坐</v>
       </c>
       <c r="E309" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F309" t="str">
-        <v>zì</v>
+        <v>zuò</v>
       </c>
       <c r="G309" t="str">
-        <v>chữ cái</v>
+        <v>Ngồi</v>
       </c>
       <c r="H309" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>8. Giao thông &amp; Di chuyển</v>
       </c>
     </row>
     <row r="310">
       <c r="A310">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B310">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="C310" t="str">
-        <v>我看了一个电影</v>
+        <v>我明天上午在学校学习</v>
       </c>
       <c r="D310" t="str">
-        <v>汉语</v>
+        <v>做</v>
       </c>
       <c r="E310" t="str">
-        <v>Danh từ</v>
+        <v>Động từ</v>
       </c>
       <c r="F310" t="str">
-        <v>hànyǔ</v>
+        <v>zuò</v>
       </c>
       <c r="G310" t="str">
-        <v>Tiếng Trung</v>
+        <v>Làm, tham gia</v>
       </c>
       <c r="H310" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
+        <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
     <row r="311">
       <c r="A311">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B311">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C311" t="str">
-        <v>我看了一个电影</v>
+        <v>今天我休息</v>
       </c>
       <c r="D311" t="str">
-        <v>汉字</v>
-      </c>
-      <c r="E311" t="str">
-        <v>Danh từ</v>
+        <v>做饭</v>
       </c>
       <c r="F311" t="str">
-        <v>hànzì</v>
+        <v>zuò fàn</v>
       </c>
       <c r="G311" t="str">
-        <v>Hán tự, chữ cái tiếng Trung</v>
+        <v>nấu cơm; nấu ăn</v>
       </c>
       <c r="H311" t="str">
-        <v>6. Đồ vật &amp; Công cụ</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312">
-        <v>311</v>
-      </c>
-      <c r="B312">
-        <v>11</v>
-      </c>
-      <c r="C312" t="str">
-        <v>我读大学了</v>
-      </c>
-      <c r="D312" t="str">
-        <v>昨天</v>
-      </c>
-      <c r="E312" t="str">
-        <v>Danh từ</v>
-      </c>
-      <c r="F312" t="str">
-        <v>zuótiān</v>
-      </c>
-      <c r="G312" t="str">
-        <v>hôm qua</v>
-      </c>
-      <c r="H312" t="str">
-        <v>10. Thời gian</v>
-      </c>
-    </row>
-    <row r="313" xml:space="preserve">
-      <c r="A313">
-        <v>312</v>
-      </c>
-      <c r="B313">
-        <v>6.13</v>
-      </c>
-      <c r="C313" t="str" xml:space="preserve">
-        <v xml:space="preserve">你的手机号码是多少_x000d_
-请给我一杯茶</v>
-      </c>
-      <c r="D313" t="str">
-        <v>坐</v>
-      </c>
-      <c r="E313" t="str">
-        <v>Động từ</v>
-      </c>
-      <c r="F313" t="str">
-        <v>zuò</v>
-      </c>
-      <c r="G313" t="str">
-        <v>Ngồi</v>
-      </c>
-      <c r="H313" t="str">
-        <v>8. Giao thông &amp; Di chuyển</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314">
-        <v>313</v>
-      </c>
-      <c r="B314">
-        <v>5.9</v>
-      </c>
-      <c r="C314" t="str">
-        <v>我明天上午在学校学习</v>
-      </c>
-      <c r="D314" t="str">
-        <v>做</v>
-      </c>
-      <c r="E314" t="str">
-        <v>Động từ</v>
-      </c>
-      <c r="F314" t="str">
-        <v>zuò</v>
-      </c>
-      <c r="G314" t="str">
-        <v>Làm, tham gia</v>
-      </c>
-      <c r="H314" t="str">
-        <v>5. Đời sống sinh hoạt</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315">
-        <v>314</v>
-      </c>
-      <c r="B315">
-        <v>5</v>
-      </c>
-      <c r="C315" t="str">
-        <v>今天我休息</v>
-      </c>
-      <c r="D315" t="str">
-        <v>做饭</v>
-      </c>
-      <c r="F315" t="str">
-        <v>zuò fàn</v>
-      </c>
-      <c r="G315" t="str">
-        <v>nấu cơm; nấu ăn</v>
-      </c>
-      <c r="H315" t="str">
         <v>5. Đời sống sinh hoạt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K315"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K311"/>
   </ignoredErrors>
 </worksheet>
 </file>
